--- a/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F53BAA5-E49E-4A95-812E-49ADC0819EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EDB673-1313-4139-8C7B-49FC0A9B9AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="76">
   <si>
     <t>Booking</t>
   </si>
@@ -254,9 +254,6 @@
   </si>
   <si>
     <t>Not Available</t>
-  </si>
-  <si>
-    <t>Resigned</t>
   </si>
 </sst>
 </file>
@@ -916,7 +913,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1221,6 +1218,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3836,15 +3834,15 @@
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>46.32</v>
+        <v>45</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>8.4218181818181817E-2</v>
+        <v>8.1818181818181818E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>503.68</v>
+        <v>505</v>
       </c>
       <c r="N6" s="14" t="e">
         <f t="shared" si="3"/>
@@ -3852,15 +3850,13 @@
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.6542857142857144</v>
+        <v>1.6071428571428572</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.8046753246753247</v>
-      </c>
-      <c r="Q6" s="34" t="s">
-        <v>76</v>
-      </c>
+        <v>1.7532467532467531</v>
+      </c>
+      <c r="Q6" s="34"/>
     </row>
     <row r="7" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -3918,9 +3914,7 @@
         <f t="shared" si="4"/>
         <v>1.4331550802139035</v>
       </c>
-      <c r="Q7" s="34" t="s">
-        <v>76</v>
-      </c>
+      <c r="Q7" s="34"/>
     </row>
     <row r="8" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -4067,15 +4061,15 @@
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <v>2232.75</v>
+        <v>2100</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.48327922077922075</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2387.25</v>
+        <v>2520</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="6"/>
@@ -4083,11 +4077,11 @@
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>22.783163265306122</v>
+        <v>21.428571428571427</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.98628412403922605</v>
+        <v>0.92764378478664189</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4251,7 +4245,7 @@
         <f t="shared" ref="P13:P16" si="11">L13/I13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q13" s="34"/>
+      <c r="Q13" s="112"/>
     </row>
     <row r="14" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A14" s="35" t="s">
@@ -4372,7 +4366,7 @@
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="70" t="e">
         <f t="shared" ref="I16" si="12">H16/G16</f>
@@ -4398,7 +4392,7 @@
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
-        <v>475</v>
+        <v>316.66666666666669</v>
       </c>
       <c r="P16" s="14" t="e">
         <f t="shared" si="11"/>
@@ -4501,11 +4495,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.17960000000000001</v>
+        <v>0.17979999999999999</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4513,15 +4507,15 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>4178.37</v>
+        <v>4044.3</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.39159981255857546</v>
+        <v>0.37903467666354268</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>6491.63</v>
+        <v>6625.7</v>
       </c>
       <c r="N19" s="83" t="e">
         <f t="shared" si="6"/>
@@ -4529,7 +4523,7 @@
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>4.6529732739420933</v>
+        <v>4.4986651835372635</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -5172,11 +5166,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.20165137614678899</v>
+        <v>0.20183486238532111</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5184,15 +5178,15 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>4457.37</v>
+        <v>4323.3</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.28445245692405868</v>
+        <v>0.27589661774090618</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>11212.630000000001</v>
+        <v>11346.7</v>
       </c>
       <c r="N31" s="92" t="e">
         <f t="shared" si="6"/>
@@ -5200,7 +5194,7 @@
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>4.0558416742493177</v>
+        <v>3.9302727272727274</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EDB673-1313-4139-8C7B-49FC0A9B9AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C86CF6-54AE-482F-9AA5-CBD271326ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1176,6 +1176,7 @@
     <xf numFmtId="1" fontId="0" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1218,7 +1219,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1526,53 +1526,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="101" t="s">
+      <c r="G1" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="104" t="s">
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="107"/>
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
         <v>46231</v>
       </c>
-      <c r="G2" s="107" t="s">
+      <c r="G2" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="108"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="108" t="s">
+      <c r="H2" s="109"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="108"/>
-      <c r="L2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="110"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="107" t="s">
+      <c r="O2" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="108" t="s">
+      <c r="P2" s="109"/>
+      <c r="Q2" s="110"/>
+      <c r="R2" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="108"/>
-      <c r="T2" s="109"/>
+      <c r="S2" s="109"/>
+      <c r="T2" s="110"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -2543,11 +2543,11 @@
       <c r="C19" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="98" t="s">
+      <c r="D19" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="99"/>
-      <c r="F19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="101"/>
       <c r="G19" s="40">
         <f>SUM(G4:G18)</f>
         <v>375</v>
@@ -3014,11 +3014,11 @@
       <c r="C25" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="98" t="s">
+      <c r="D25" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="99"/>
-      <c r="F25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="101"/>
       <c r="G25" s="40">
         <f>SUM(G20:G24)</f>
         <v>250</v>
@@ -3395,11 +3395,11 @@
       <c r="C30" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="98" t="s">
+      <c r="D30" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="99"/>
-      <c r="F30" s="100"/>
+      <c r="E30" s="100"/>
+      <c r="F30" s="101"/>
       <c r="G30" s="40">
         <f>SUM(G26:G29)</f>
         <v>2400</v>
@@ -3615,22 +3615,22 @@
       <c r="F2" s="94">
         <v>46234</v>
       </c>
-      <c r="G2" s="107" t="s">
+      <c r="G2" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="104" t="s">
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="110" t="s">
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="111"/>
+      <c r="P2" s="112"/>
     </row>
     <row r="3" spans="1:17" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="25" t="s">
@@ -3708,26 +3708,25 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11+8+11+8+16+14+16+20+15+10+10+16+12+20</f>
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.4</v>
+        <v>0.37333333333333335</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>335</v>
+        <v>267.3</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.58260869565217388</v>
+        <v>0.46486956521739131</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>240</v>
+        <v>307.7</v>
       </c>
       <c r="N4" s="10" t="e">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
@@ -3735,7 +3734,7 @@
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.3958333333333333</v>
+        <v>1.1933035714285716</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -4108,26 +4107,25 @@
         <v>600</v>
       </c>
       <c r="H11" s="12">
-        <f>12+0</f>
-        <v>12</v>
+        <v>225</v>
       </c>
       <c r="I11" s="70">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.375</v>
       </c>
       <c r="J11" s="11">
         <v>650</v>
       </c>
       <c r="K11" s="12">
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="L11" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.77076923076923076</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="5"/>
-        <v>650</v>
+        <v>149</v>
       </c>
       <c r="N11" s="14" t="e">
         <f t="shared" si="6"/>
@@ -4135,11 +4133,11 @@
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.2266666666666666</v>
       </c>
       <c r="P11" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.0553846153846154</v>
       </c>
       <c r="Q11" s="34"/>
     </row>
@@ -4166,25 +4164,25 @@
         <v>600</v>
       </c>
       <c r="H12" s="12">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="I12" s="70">
         <f t="shared" si="0"/>
-        <v>4.6666666666666669E-2</v>
+        <v>0.19166666666666668</v>
       </c>
       <c r="J12" s="11">
         <v>550</v>
       </c>
       <c r="K12" s="12">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="L12" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.27454545454545454</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="5"/>
-        <v>550</v>
+        <v>399</v>
       </c>
       <c r="N12" s="14" t="e">
         <f t="shared" si="6"/>
@@ -4192,11 +4190,11 @@
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.3130434782608695</v>
       </c>
       <c r="P12" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.4324110671936758</v>
       </c>
       <c r="Q12" s="34"/>
     </row>
@@ -4245,7 +4243,7 @@
         <f t="shared" ref="P13:P16" si="11">L13/I13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q13" s="112"/>
+      <c r="Q13" s="98"/>
     </row>
     <row r="14" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A14" s="35" t="s">
@@ -4484,22 +4482,22 @@
       <c r="C19" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="98" t="s">
+      <c r="D19" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="99"/>
-      <c r="F19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="101"/>
       <c r="G19" s="40">
         <f>SUM(G4:G18)</f>
         <v>5000</v>
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>899</v>
+        <v>1183</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.17979999999999999</v>
+        <v>0.2366</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4507,15 +4505,15 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>4044.3</v>
+        <v>4628.6000000000004</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.37903467666354268</v>
+        <v>0.43379568884723529</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>6625.7</v>
+        <v>6041.4</v>
       </c>
       <c r="N19" s="83" t="e">
         <f t="shared" si="6"/>
@@ -4523,7 +4521,7 @@
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>4.4986651835372635</v>
+        <v>3.9125950972104819</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4821,11 +4819,11 @@
       <c r="C25" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="98" t="s">
+      <c r="D25" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="99"/>
-      <c r="F25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="101"/>
       <c r="G25" s="40">
         <f>SUM(G20:G24)</f>
         <v>250</v>
@@ -5102,11 +5100,11 @@
       <c r="C30" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="98" t="s">
+      <c r="D30" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="99"/>
-      <c r="F30" s="100"/>
+      <c r="E30" s="100"/>
+      <c r="F30" s="101"/>
       <c r="G30" s="40">
         <f>SUM(G26:G29)</f>
         <v>200</v>
@@ -5166,11 +5164,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>1100</v>
+        <v>1384</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.20183486238532111</v>
+        <v>0.25394495412844037</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5178,15 +5176,15 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>4323.3</v>
+        <v>4907.6000000000004</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.27589661774090618</v>
+        <v>0.31318442884492664</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>11346.7</v>
+        <v>10762.4</v>
       </c>
       <c r="N31" s="92" t="e">
         <f t="shared" si="6"/>
@@ -5194,7 +5192,7 @@
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.9302727272727274</v>
+        <v>3.5459537572254338</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C86CF6-54AE-482F-9AA5-CBD271326ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659FF0BD-BCB1-452A-92C6-C18917B309E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3708,25 +3708,25 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <v>224</v>
+        <v>325</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.37333333333333335</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>267.3</v>
+        <v>335</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.46486956521739131</v>
+        <v>0.58260869565217388</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>307.7</v>
+        <v>240</v>
       </c>
       <c r="N4" s="10" t="e">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1933035714285716</v>
+        <v>1.0307692307692307</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -4493,11 +4493,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>1183</v>
+        <v>1284</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.2366</v>
+        <v>0.25679999999999997</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4505,15 +4505,15 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>4628.6000000000004</v>
+        <v>4696.3</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.43379568884723529</v>
+        <v>0.44014058106841614</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>6041.4</v>
+        <v>5973.7</v>
       </c>
       <c r="N19" s="83" t="e">
         <f t="shared" si="6"/>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.9125950972104819</v>
+        <v>3.6575545171339567</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -5164,11 +5164,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>1384</v>
+        <v>1485</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.25394495412844037</v>
+        <v>0.27247706422018347</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5176,15 +5176,15 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>4907.6000000000004</v>
+        <v>4975.3</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.31318442884492664</v>
+        <v>0.31750478621569878</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>10762.4</v>
+        <v>10694.7</v>
       </c>
       <c r="N31" s="92" t="e">
         <f t="shared" si="6"/>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.5459537572254338</v>
+        <v>3.3503703703703707</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659FF0BD-BCB1-452A-92C6-C18917B309E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761ADEF0-8597-47B5-9B2C-DC5B6E0EA364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761ADEF0-8597-47B5-9B2C-DC5B6E0EA364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CDAAC2-2843-4F21-948C-F7FDB6FBC739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CDAAC2-2843-4F21-948C-F7FDB6FBC739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA6FB62-9AD1-450A-A0C4-3692CC1A1A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Behind/july 2026/Daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA6FB62-9AD1-450A-A0C4-3692CC1A1A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67D1115-B2CD-42D9-B3D7-5CD9F8D0BCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
